--- a/metadata/Data 2024 For Syl Segmentation_1.xlsx
+++ b/metadata/Data 2024 For Syl Segmentation_1.xlsx
@@ -489,7 +489,7 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -523,7 +523,7 @@
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -557,7 +557,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -591,7 +591,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -625,7 +625,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -659,7 +659,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -693,7 +693,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -727,7 +727,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -761,7 +761,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -795,7 +795,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -829,7 +829,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -863,7 +863,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -897,7 +897,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -931,7 +931,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -965,7 +965,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -999,7 +999,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -1033,7 +1033,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -1067,7 +1067,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -1101,7 +1101,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -1135,7 +1135,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -1169,7 +1169,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -1203,7 +1203,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1237,7 +1237,7 @@
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1271,7 +1271,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1305,7 +1305,7 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -1339,7 +1339,7 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -1373,7 +1373,7 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -1407,7 +1407,7 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1441,7 +1441,7 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -1475,7 +1475,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -1509,7 +1509,7 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -1543,7 +1543,7 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1577,7 +1577,7 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1611,7 +1611,7 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -1645,7 +1645,7 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1679,7 +1679,7 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -1713,7 +1713,7 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -1747,7 +1747,7 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1781,7 +1781,7 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1815,7 +1815,7 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1849,7 +1849,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1883,7 +1883,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1917,7 +1917,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1951,7 +1951,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1985,7 +1985,7 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2019,7 +2019,7 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2053,7 +2053,7 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2087,7 +2087,7 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2121,7 +2121,7 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2155,7 +2155,7 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2189,7 +2189,7 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2223,7 +2223,7 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2257,7 +2257,7 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2291,7 +2291,7 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2325,7 +2325,7 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2359,7 +2359,7 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2393,7 +2393,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2427,7 +2427,7 @@
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2461,7 +2461,7 @@
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2495,7 +2495,7 @@
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -2529,7 +2529,7 @@
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -2563,7 +2563,7 @@
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -2597,7 +2597,7 @@
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -2631,7 +2631,7 @@
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -2665,7 +2665,7 @@
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2699,7 +2699,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2733,7 +2733,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -2767,7 +2767,7 @@
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -2801,7 +2801,7 @@
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -2835,7 +2835,7 @@
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -2869,7 +2869,7 @@
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -2903,7 +2903,7 @@
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -2937,7 +2937,7 @@
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -2971,7 +2971,7 @@
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -3005,7 +3005,7 @@
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -3039,7 +3039,7 @@
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -3073,7 +3073,7 @@
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F78" t="n">
@@ -3107,7 +3107,7 @@
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -3141,7 +3141,7 @@
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F80" t="n">
@@ -3175,7 +3175,7 @@
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -3209,7 +3209,7 @@
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F82" t="n">
@@ -3243,7 +3243,7 @@
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -3277,7 +3277,7 @@
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -3311,7 +3311,7 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -3345,7 +3345,7 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -3379,7 +3379,7 @@
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3413,7 +3413,7 @@
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F88" t="n">
@@ -3447,7 +3447,7 @@
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3481,7 +3481,7 @@
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F90" t="n">
@@ -3515,7 +3515,7 @@
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3549,7 +3549,7 @@
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F92" t="n">
@@ -3583,7 +3583,7 @@
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3617,7 +3617,7 @@
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3651,7 +3651,7 @@
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3685,7 +3685,7 @@
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3719,7 +3719,7 @@
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3753,7 +3753,7 @@
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3787,7 +3787,7 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -3821,7 +3821,7 @@
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F100" t="n">
@@ -3855,7 +3855,7 @@
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -3889,7 +3889,7 @@
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F102" t="n">
@@ -3923,7 +3923,7 @@
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F103" t="n">
@@ -3957,7 +3957,7 @@
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F104" t="n">
@@ -3991,7 +3991,7 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F105" t="n">
@@ -4025,7 +4025,7 @@
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F106" t="n">
@@ -4059,7 +4059,7 @@
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -4093,7 +4093,7 @@
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F108" t="n">
@@ -4127,7 +4127,7 @@
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F109" t="n">
@@ -4161,7 +4161,7 @@
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F110" t="n">
@@ -4195,7 +4195,7 @@
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F111" t="n">
@@ -4229,7 +4229,7 @@
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F112" t="n">
@@ -4263,7 +4263,7 @@
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F113" t="n">
@@ -4297,7 +4297,7 @@
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F114" t="n">
@@ -4331,7 +4331,7 @@
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F115" t="n">
@@ -4365,7 +4365,7 @@
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -4399,7 +4399,7 @@
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F117" t="n">
@@ -4433,7 +4433,7 @@
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F118" t="n">
@@ -4467,7 +4467,7 @@
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -4501,7 +4501,7 @@
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F120" t="n">
@@ -4535,7 +4535,7 @@
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -4569,7 +4569,7 @@
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F122" t="n">
@@ -4603,7 +4603,7 @@
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F123" t="n">
@@ -4637,7 +4637,7 @@
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F124" t="n">
@@ -4671,7 +4671,7 @@
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F125" t="n">
@@ -4705,7 +4705,7 @@
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F126" t="n">
@@ -4739,7 +4739,7 @@
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F127" t="n">
@@ -4773,7 +4773,7 @@
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F128" t="n">
@@ -4807,7 +4807,7 @@
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F129" t="n">
@@ -4841,7 +4841,7 @@
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F130" t="n">
@@ -4875,7 +4875,7 @@
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F131" t="n">
@@ -4909,7 +4909,7 @@
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F132" t="n">
@@ -4943,7 +4943,7 @@
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F133" t="n">
@@ -4977,7 +4977,7 @@
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F134" t="n">
@@ -5011,7 +5011,7 @@
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F135" t="n">
@@ -5045,7 +5045,7 @@
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -5079,7 +5079,7 @@
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F137" t="n">
@@ -5113,7 +5113,7 @@
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F138" t="n">
@@ -5147,7 +5147,7 @@
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -5181,7 +5181,7 @@
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F140" t="n">
@@ -5215,7 +5215,7 @@
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F141" t="n">
@@ -5249,7 +5249,7 @@
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F142" t="n">
@@ -5283,7 +5283,7 @@
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F143" t="n">
@@ -5317,7 +5317,7 @@
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -5351,7 +5351,7 @@
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -5385,7 +5385,7 @@
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F146" t="n">
@@ -5419,7 +5419,7 @@
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F147" t="n">
@@ -5453,7 +5453,7 @@
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F148" t="n">
@@ -5487,7 +5487,7 @@
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F149" t="n">
@@ -5521,7 +5521,7 @@
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F150" t="n">
@@ -5555,7 +5555,7 @@
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F151" t="n">
@@ -5589,7 +5589,7 @@
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F152" t="n">
@@ -5623,7 +5623,7 @@
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F153" t="n">
@@ -5657,7 +5657,7 @@
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -5691,7 +5691,7 @@
       <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -5725,7 +5725,7 @@
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F156" t="n">
@@ -5759,7 +5759,7 @@
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F157" t="n">
@@ -5793,7 +5793,7 @@
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F158" t="n">
@@ -5827,7 +5827,7 @@
       <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F159" t="n">
@@ -5861,7 +5861,7 @@
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F160" t="n">
@@ -5895,7 +5895,7 @@
       <c r="D161" t="inlineStr"/>
       <c r="E161" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F161" t="n">
@@ -5929,7 +5929,7 @@
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F162" t="n">
@@ -5963,7 +5963,7 @@
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F163" t="n">
@@ -5997,7 +5997,7 @@
       <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -6031,7 +6031,7 @@
       <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -6065,7 +6065,7 @@
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F166" t="n">
@@ -6099,7 +6099,7 @@
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F167" t="n">
@@ -6133,7 +6133,7 @@
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -6167,7 +6167,7 @@
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F169" t="n">
@@ -6201,7 +6201,7 @@
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F170" t="n">
@@ -6235,7 +6235,7 @@
       <c r="D171" t="inlineStr"/>
       <c r="E171" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F171" t="n">
@@ -6269,7 +6269,7 @@
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F172" t="n">
@@ -6303,7 +6303,7 @@
       <c r="D173" t="inlineStr"/>
       <c r="E173" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F173" t="n">
@@ -6337,7 +6337,7 @@
       <c r="D174" t="inlineStr"/>
       <c r="E174" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -6371,7 +6371,7 @@
       <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -6405,7 +6405,7 @@
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F176" t="n">
@@ -6439,7 +6439,7 @@
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F177" t="n">
@@ -6473,7 +6473,7 @@
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F178" t="n">
@@ -6507,7 +6507,7 @@
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F179" t="n">
@@ -6541,7 +6541,7 @@
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F180" t="n">
@@ -6575,7 +6575,7 @@
       <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F181" t="n">
@@ -6609,7 +6609,7 @@
       <c r="D182" t="inlineStr"/>
       <c r="E182" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F182" t="n">
@@ -6643,7 +6643,7 @@
       <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F183" t="n">
@@ -6677,7 +6677,7 @@
       <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -6711,7 +6711,7 @@
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -6745,7 +6745,7 @@
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F186" t="n">
@@ -6779,7 +6779,7 @@
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -6813,7 +6813,7 @@
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F188" t="n">
@@ -6847,7 +6847,7 @@
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F189" t="n">
@@ -6881,7 +6881,7 @@
       <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F190" t="n">
@@ -6915,7 +6915,7 @@
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F191" t="n">
@@ -6949,7 +6949,7 @@
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F192" t="n">
@@ -6983,7 +6983,7 @@
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F193" t="n">
@@ -7017,7 +7017,7 @@
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -7051,7 +7051,7 @@
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -7085,7 +7085,7 @@
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F196" t="n">
@@ -7119,7 +7119,7 @@
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F197" t="n">
@@ -7153,7 +7153,7 @@
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -7187,7 +7187,7 @@
       <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F199" t="n">
@@ -7221,7 +7221,7 @@
       <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F200" t="n">
@@ -7255,7 +7255,7 @@
       <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F201" t="n">
@@ -7289,7 +7289,7 @@
       <c r="D202" t="inlineStr"/>
       <c r="E202" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F202" t="n">
@@ -7323,7 +7323,7 @@
       <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -7357,7 +7357,7 @@
       <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -7391,7 +7391,7 @@
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -7425,7 +7425,7 @@
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F206" t="n">
@@ -7459,7 +7459,7 @@
       <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F207" t="n">
@@ -7493,7 +7493,7 @@
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F208" t="n">
@@ -7527,7 +7527,7 @@
       <c r="D209" t="inlineStr"/>
       <c r="E209" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F209" t="n">
@@ -7561,7 +7561,7 @@
       <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F210" t="n">
@@ -7595,7 +7595,7 @@
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F211" t="n">
@@ -7629,7 +7629,7 @@
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F212" t="n">
@@ -7663,7 +7663,7 @@
       <c r="D213" t="inlineStr"/>
       <c r="E213" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F213" t="n">
@@ -7697,7 +7697,7 @@
       <c r="D214" t="inlineStr"/>
       <c r="E214" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -7731,7 +7731,7 @@
       <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F215" t="n">
@@ -7765,7 +7765,7 @@
       <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F216" t="n">
@@ -7799,7 +7799,7 @@
       <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F217" t="n">
@@ -7833,7 +7833,7 @@
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F218" t="n">
@@ -7867,7 +7867,7 @@
       <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F219" t="n">
@@ -7901,7 +7901,7 @@
       <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F220" t="n">
@@ -7935,7 +7935,7 @@
       <c r="D221" t="inlineStr"/>
       <c r="E221" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F221" t="n">
@@ -7969,7 +7969,7 @@
       <c r="D222" t="inlineStr"/>
       <c r="E222" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F222" t="n">
@@ -8003,7 +8003,7 @@
       <c r="D223" t="inlineStr"/>
       <c r="E223" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F223" t="n">
@@ -8037,7 +8037,7 @@
       <c r="D224" t="inlineStr"/>
       <c r="E224" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F224" t="n">
@@ -8071,7 +8071,7 @@
       <c r="D225" t="inlineStr"/>
       <c r="E225" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F225" t="n">
@@ -8105,7 +8105,7 @@
       <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -8139,7 +8139,7 @@
       <c r="D227" t="inlineStr"/>
       <c r="E227" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F227" t="n">
@@ -8173,7 +8173,7 @@
       <c r="D228" t="inlineStr"/>
       <c r="E228" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F228" t="n">
@@ -8207,7 +8207,7 @@
       <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F229" t="n">
@@ -8241,7 +8241,7 @@
       <c r="D230" t="inlineStr"/>
       <c r="E230" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F230" t="n">
@@ -8275,7 +8275,7 @@
       <c r="D231" t="inlineStr"/>
       <c r="E231" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F231" t="n">
@@ -8309,7 +8309,7 @@
       <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F232" t="n">
@@ -8343,7 +8343,7 @@
       <c r="D233" t="inlineStr"/>
       <c r="E233" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F233" t="n">
@@ -8377,7 +8377,7 @@
       <c r="D234" t="inlineStr"/>
       <c r="E234" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F234" t="n">
@@ -8411,7 +8411,7 @@
       <c r="D235" t="inlineStr"/>
       <c r="E235" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F235" t="n">
@@ -8445,7 +8445,7 @@
       <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F236" t="n">
@@ -8479,7 +8479,7 @@
       <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F237" t="n">
@@ -8513,7 +8513,7 @@
       <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F238" t="n">
@@ -8547,7 +8547,7 @@
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -8581,7 +8581,7 @@
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F240" t="n">
@@ -8615,7 +8615,7 @@
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F241" t="n">
@@ -8649,7 +8649,7 @@
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F242" t="n">
@@ -8683,7 +8683,7 @@
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F243" t="n">
@@ -8717,7 +8717,7 @@
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F244" t="n">
@@ -8751,7 +8751,7 @@
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F245" t="n">
@@ -8785,7 +8785,7 @@
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F246" t="n">
@@ -8819,7 +8819,7 @@
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F247" t="n">
@@ -8853,7 +8853,7 @@
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F248" t="n">
@@ -8887,7 +8887,7 @@
       <c r="D249" t="inlineStr"/>
       <c r="E249" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F249" t="n">
@@ -8921,7 +8921,7 @@
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F250" t="n">
@@ -8955,7 +8955,7 @@
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F251" t="n">
@@ -8989,7 +8989,7 @@
       <c r="D252" t="inlineStr"/>
       <c r="E252" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F252" t="n">
@@ -9023,7 +9023,7 @@
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F253" t="n">
@@ -9057,7 +9057,7 @@
       <c r="D254" t="inlineStr"/>
       <c r="E254" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F254" t="n">
@@ -9091,7 +9091,7 @@
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F255" t="n">
@@ -9125,7 +9125,7 @@
       <c r="D256" t="inlineStr"/>
       <c r="E256" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F256" t="n">
@@ -9159,7 +9159,7 @@
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F257" t="n">
@@ -9193,7 +9193,7 @@
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -9227,7 +9227,7 @@
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F259" t="n">
@@ -9261,7 +9261,7 @@
       <c r="D260" t="inlineStr"/>
       <c r="E260" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F260" t="n">
@@ -9295,7 +9295,7 @@
       <c r="D261" t="inlineStr"/>
       <c r="E261" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F261" t="n">
@@ -9329,7 +9329,7 @@
       <c r="D262" t="inlineStr"/>
       <c r="E262" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F262" t="n">
@@ -9363,7 +9363,7 @@
       <c r="D263" t="inlineStr"/>
       <c r="E263" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F263" t="n">
@@ -9397,7 +9397,7 @@
       <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F264" t="n">
@@ -9431,7 +9431,7 @@
       <c r="D265" t="inlineStr"/>
       <c r="E265" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F265" t="n">
@@ -9465,7 +9465,7 @@
       <c r="D266" t="inlineStr"/>
       <c r="E266" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F266" t="n">
@@ -9499,7 +9499,7 @@
       <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F267" t="n">
@@ -9533,7 +9533,7 @@
       <c r="D268" t="inlineStr"/>
       <c r="E268" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F268" t="n">
@@ -9567,7 +9567,7 @@
       <c r="D269" t="inlineStr"/>
       <c r="E269" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F269" t="n">
@@ -9601,7 +9601,7 @@
       <c r="D270" t="inlineStr"/>
       <c r="E270" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F270" t="n">
@@ -9635,7 +9635,7 @@
       <c r="D271" t="inlineStr"/>
       <c r="E271" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F271" t="n">
@@ -9669,7 +9669,7 @@
       <c r="D272" t="inlineStr"/>
       <c r="E272" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F272" t="n">
@@ -9703,7 +9703,7 @@
       <c r="D273" t="inlineStr"/>
       <c r="E273" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F273" t="n">
@@ -9737,7 +9737,7 @@
       <c r="D274" t="inlineStr"/>
       <c r="E274" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F274" t="n">
@@ -9771,7 +9771,7 @@
       <c r="D275" t="inlineStr"/>
       <c r="E275" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F275" t="n">
@@ -9805,7 +9805,7 @@
       <c r="D276" t="inlineStr"/>
       <c r="E276" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F276" t="n">
@@ -9839,7 +9839,7 @@
       <c r="D277" t="inlineStr"/>
       <c r="E277" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F277" t="n">
@@ -9873,7 +9873,7 @@
       <c r="D278" t="inlineStr"/>
       <c r="E278" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F278" t="n">
@@ -9907,7 +9907,7 @@
       <c r="D279" t="inlineStr"/>
       <c r="E279" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F279" t="n">
@@ -9941,7 +9941,7 @@
       <c r="D280" t="inlineStr"/>
       <c r="E280" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F280" t="n">
@@ -9975,7 +9975,7 @@
       <c r="D281" t="inlineStr"/>
       <c r="E281" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F281" t="n">
@@ -10009,7 +10009,7 @@
       <c r="D282" t="inlineStr"/>
       <c r="E282" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -10043,7 +10043,7 @@
       <c r="D283" t="inlineStr"/>
       <c r="E283" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F283" t="n">
@@ -10077,7 +10077,7 @@
       <c r="D284" t="inlineStr"/>
       <c r="E284" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F284" t="n">
@@ -10111,7 +10111,7 @@
       <c r="D285" t="inlineStr"/>
       <c r="E285" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F285" t="n">
@@ -10145,7 +10145,7 @@
       <c r="D286" t="inlineStr"/>
       <c r="E286" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F286" t="n">
@@ -10179,7 +10179,7 @@
       <c r="D287" t="inlineStr"/>
       <c r="E287" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F287" t="n">
@@ -10213,7 +10213,7 @@
       <c r="D288" t="inlineStr"/>
       <c r="E288" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F288" t="n">
@@ -10247,7 +10247,7 @@
       <c r="D289" t="inlineStr"/>
       <c r="E289" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F289" t="n">
@@ -10281,7 +10281,7 @@
       <c r="D290" t="inlineStr"/>
       <c r="E290" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F290" t="n">
@@ -10315,7 +10315,7 @@
       <c r="D291" t="inlineStr"/>
       <c r="E291" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F291" t="n">
@@ -10349,7 +10349,7 @@
       <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F292" t="n">
@@ -10383,7 +10383,7 @@
       <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F293" t="n">
@@ -10417,7 +10417,7 @@
       <c r="D294" t="inlineStr"/>
       <c r="E294" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F294" t="n">
@@ -10451,7 +10451,7 @@
       <c r="D295" t="inlineStr"/>
       <c r="E295" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F295" t="n">
@@ -10485,7 +10485,7 @@
       <c r="D296" t="inlineStr"/>
       <c r="E296" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F296" t="n">
@@ -10519,7 +10519,7 @@
       <c r="D297" t="inlineStr"/>
       <c r="E297" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F297" t="n">
@@ -10553,7 +10553,7 @@
       <c r="D298" t="inlineStr"/>
       <c r="E298" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F298" t="n">
@@ -10587,7 +10587,7 @@
       <c r="D299" t="inlineStr"/>
       <c r="E299" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F299" t="n">
@@ -10621,7 +10621,7 @@
       <c r="D300" t="inlineStr"/>
       <c r="E300" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F300" t="n">
@@ -10655,7 +10655,7 @@
       <c r="D301" t="inlineStr"/>
       <c r="E301" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F301" t="n">
@@ -10689,7 +10689,7 @@
       <c r="D302" t="inlineStr"/>
       <c r="E302" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F302" t="n">
@@ -10723,7 +10723,7 @@
       <c r="D303" t="inlineStr"/>
       <c r="E303" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F303" t="n">
@@ -10757,7 +10757,7 @@
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F304" t="n">
@@ -10791,7 +10791,7 @@
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F305" t="n">
@@ -10825,7 +10825,7 @@
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>HET</t>
+          <t>WT</t>
         </is>
       </c>
       <c r="F306" t="n">
